--- a/projetPFA/outputs/test_Machines_Test_Realiste_2.xlsx
+++ b/projetPFA/outputs/test_Machines_Test_Realiste_2.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Lignes_utiles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lignes_rejetees" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +497,7 @@
         <v>6.55</v>
       </c>
       <c r="F3" t="n">
-        <v>0.985</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +523,7 @@
         <v>10.91</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +549,7 @@
         <v>3.57</v>
       </c>
       <c r="F5" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +575,7 @@
         <v>2.94</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +627,7 @@
         <v>16.93</v>
       </c>
       <c r="F8" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +653,7 @@
         <v>10.13</v>
       </c>
       <c r="F9" t="n">
-        <v>0.975</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="10">
@@ -758,7 +757,7 @@
         <v>6.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="14">
@@ -810,7 +809,7 @@
         <v>7.71</v>
       </c>
       <c r="F15" t="n">
-        <v>0.87</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="16">
@@ -836,7 +835,7 @@
         <v>3.54</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="17">
@@ -862,7 +861,7 @@
         <v>3.36</v>
       </c>
       <c r="F17" t="n">
-        <v>0.985</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="18">
@@ -914,7 +913,7 @@
         <v>0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +939,7 @@
         <v>7.35</v>
       </c>
       <c r="F20" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +965,7 @@
         <v>7.36</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="22">
@@ -1018,7 +1017,7 @@
         <v>10.93</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="24">
@@ -1044,7 +1043,7 @@
         <v>5.91</v>
       </c>
       <c r="F24" t="n">
-        <v>0.955</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="25">
@@ -1122,7 +1121,7 @@
         <v>6.64</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="28">
@@ -1174,7 +1173,7 @@
         <v>5.64</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="30">
@@ -1200,7 +1199,7 @@
         <v>15.54</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="31">
@@ -1304,7 +1303,7 @@
         <v>0.72</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="35">
@@ -1382,7 +1381,7 @@
         <v>10.13</v>
       </c>
       <c r="F37" t="n">
-        <v>0.98</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="38">
@@ -1460,7 +1459,7 @@
         <v>2.25</v>
       </c>
       <c r="F40" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="41">
@@ -1486,7 +1485,7 @@
         <v>8.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.96</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="42">
@@ -1512,7 +1511,7 @@
         <v>1.84</v>
       </c>
       <c r="F42" t="n">
-        <v>0.975</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="43">
@@ -1538,7 +1537,7 @@
         <v>0.32</v>
       </c>
       <c r="F43" t="n">
-        <v>0.985</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1615,7 @@
         <v>6.91</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="47">
@@ -1720,7 +1719,7 @@
         <v>15.17</v>
       </c>
       <c r="F50" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1746,7 +1745,7 @@
         <v>9.27</v>
       </c>
       <c r="F51" t="n">
-        <v>0.875</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="52">
@@ -1824,7 +1823,7 @@
         <v>0.05</v>
       </c>
       <c r="F54" t="n">
-        <v>0.985</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="55">
@@ -1850,7 +1849,7 @@
         <v>0.05</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="56">
@@ -1902,7 +1901,7 @@
         <v>8.67</v>
       </c>
       <c r="F57" t="n">
-        <v>0.995</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="58">
@@ -1928,7 +1927,7 @@
         <v>11.01</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="59">
@@ -1980,7 +1979,7 @@
         <v>2.32</v>
       </c>
       <c r="F60" t="n">
-        <v>0.915</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="61">
@@ -2110,7 +2109,7 @@
         <v>12.08</v>
       </c>
       <c r="F65" t="n">
-        <v>0.985</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="66">
@@ -2136,7 +2135,7 @@
         <v>12.23</v>
       </c>
       <c r="F66" t="n">
-        <v>0.975</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="67">
@@ -2214,7 +2213,7 @@
         <v>5.99</v>
       </c>
       <c r="F69" t="n">
-        <v>0.99</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="70">
@@ -2266,7 +2265,7 @@
         <v>9.550000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2370,7 +2369,7 @@
         <v>5.79</v>
       </c>
       <c r="F75" t="n">
-        <v>0.975</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="76">
@@ -2422,7 +2421,7 @@
         <v>11.8</v>
       </c>
       <c r="F77" t="n">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="78">
@@ -2500,7 +2499,7 @@
         <v>5.68</v>
       </c>
       <c r="F80" t="n">
-        <v>0.885</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="81">
@@ -2526,7 +2525,7 @@
         <v>10.62</v>
       </c>
       <c r="F81" t="n">
-        <v>0.835</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="82">
@@ -2552,7 +2551,7 @@
         <v>12.38</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="83">
@@ -2604,7 +2603,7 @@
         <v>13.03</v>
       </c>
       <c r="F84" t="n">
-        <v>0.985</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="85">
@@ -2656,7 +2655,7 @@
         <v>12.28</v>
       </c>
       <c r="F86" t="n">
-        <v>0.99</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="87">
@@ -2734,7 +2733,7 @@
         <v>13.23</v>
       </c>
       <c r="F89" t="n">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="90">
@@ -2786,7 +2785,7 @@
         <v>8.59</v>
       </c>
       <c r="F91" t="n">
-        <v>0.925</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="92">
@@ -2864,7 +2863,7 @@
         <v>1.55</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="95">
@@ -2916,7 +2915,7 @@
         <v>6.69</v>
       </c>
       <c r="F96" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="97">
@@ -2942,7 +2941,7 @@
         <v>7.04</v>
       </c>
       <c r="F97" t="n">
-        <v>0.97</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -2968,7 +2967,7 @@
         <v>7.32</v>
       </c>
       <c r="F98" t="n">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="99">
@@ -3020,7 +3019,7 @@
         <v>14.61</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="101">
@@ -3072,7 +3071,7 @@
         <v>8.77</v>
       </c>
       <c r="F102" t="n">
-        <v>0.995</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="103">
@@ -3098,7 +3097,7 @@
         <v>3.16</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="104">
@@ -3150,7 +3149,7 @@
         <v>2.56</v>
       </c>
       <c r="F105" t="n">
-        <v>0.98</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="106">
@@ -3176,7 +3175,7 @@
         <v>6.71</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="107">
@@ -3202,7 +3201,7 @@
         <v>10.78</v>
       </c>
       <c r="F107" t="n">
-        <v>0.98</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="108">
@@ -3228,7 +3227,7 @@
         <v>4.37</v>
       </c>
       <c r="F108" t="n">
-        <v>0.98</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="109">
@@ -3280,7 +3279,7 @@
         <v>14.71</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="111">
@@ -3332,7 +3331,7 @@
         <v>9.52</v>
       </c>
       <c r="F112" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="113">
@@ -3358,7 +3357,7 @@
         <v>7.1</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="114">
@@ -3410,7 +3409,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>0.92</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="116">
@@ -3436,7 +3435,7 @@
         <v>6.03</v>
       </c>
       <c r="F116" t="n">
-        <v>0.965</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="117">
@@ -3488,7 +3487,7 @@
         <v>9.34</v>
       </c>
       <c r="F118" t="n">
-        <v>0.775</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="119">
@@ -3514,7 +3513,7 @@
         <v>7.9</v>
       </c>
       <c r="F119" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="120">
@@ -3592,7 +3591,7 @@
         <v>7.67</v>
       </c>
       <c r="F122" t="n">
-        <v>0.885</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="123">
@@ -3644,7 +3643,7 @@
         <v>12.4</v>
       </c>
       <c r="F124" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="125">
@@ -3670,7 +3669,7 @@
         <v>15.77</v>
       </c>
       <c r="F125" t="n">
-        <v>0.95</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="126">
@@ -3696,7 +3695,7 @@
         <v>0.05</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="127">
@@ -3748,7 +3747,7 @@
         <v>13.3</v>
       </c>
       <c r="F128" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="129">
@@ -3827,739 +3826,6 @@
       </c>
       <c r="F131" t="n">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>HeuresFonctionnement</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TauxDefaut_%</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>utilite_predite</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score_confiance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Testeur fonctionnel_170708</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Robot de soudure_775886</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Assembly board to board_301013</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_587707</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_130703</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_124776</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SMC Adaptor_122845</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Assembly board to board_253493</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Packing</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_928885</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Packing</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Camera inspection_479919</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Camera inspection_832516</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Packing</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Station de vissage_214303</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SMT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0.885</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Convoyeur_651842</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_426857</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Camera inspection_185031</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Camera inspection_488201</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Camera inspection_797611</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Optimel Ferite_414939</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SMC Adaptor_935782</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SMC Adaptor_829623</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Testeur fonctionnel_416167</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Assembly board to board_296412</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SMT</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3720.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0.885</v>
       </c>
     </row>
   </sheetData>
